--- a/data/TestMultiKey.xlsx
+++ b/data/TestMultiKey.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD12"/>
+  <dimension ref="A1:AD11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,42 +424,12 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>tag1_key</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>tag1_value</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>tag1_key</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>tag1_value</t>
+          <t>tag1</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>immunetag1_key</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>immunetag1_value</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>immunetag1_key</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>immunetag1_value</t>
+          <t>immunetag1</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -469,70 +439,10 @@
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>testobj1_key</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>testobj1_value</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>testobj1_key</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>testobj1_value</t>
-        </is>
-      </c>
-      <c r="O1" t="inlineStr">
-        <is>
-          <t>testobj1_key</t>
-        </is>
-      </c>
-      <c r="P1" t="inlineStr">
-        <is>
-          <t>testobj1_value</t>
-        </is>
-      </c>
-      <c r="Q1" t="inlineStr">
-        <is>
-          <t>testobj1_key</t>
-        </is>
-      </c>
-      <c r="R1" t="inlineStr">
-        <is>
-          <t>testobj1_value</t>
+          <t>testobj1</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>effect</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
         <is>
           <t>effect</t>
         </is>
@@ -576,42 +486,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>string</t>
+          <t>map&lt;string,string&gt;</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>string</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>string</t>
+          <t>map&lt;string,string&gt;</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -621,72 +501,12 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>uint32</t>
+          <t>repeated { uint32 key; uint32 value }</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>uint32</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>uint32</t>
+          <t>repeated uint32</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -721,380 +541,235 @@
       </c>
     </row>
     <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>map_key</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>map_value</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>map_key</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>map_value</t>
+          <t>common</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>map_key</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>map_value</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>map_key</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>map_value</t>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>message:testobj1</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>message:testobj1</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>message:testobj1</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>message:testobj1</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>message:testobj1</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>message:testobj1</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>message:testobj1</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>message:testobj1</t>
+          <t>common</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>repeated</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>repeated</t>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>common</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>common</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>common</t>
+          <t>multi</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>key</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>key</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>key</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>multi key</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>multi key</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>common</t>
+          <t>multi key</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>multi</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>key</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>multi key</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>multi key</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>multi key</t>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>免疫tag</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>等级</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>等级</t>
         </is>
       </c>
     </row>
     <row r="6">
+      <c r="A6" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Metal</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>免疫tag</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>免疫tag</t>
+          <t>None</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>免疫tag</t>
+          <t>Control</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>免疫tag</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>等级</t>
-        </is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>aa</t>
+        </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>14</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>aa</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>17</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1104,12 +779,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -1128,19 +803,19 @@
         </is>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1155,10 +830,10 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1174,18 +849,18 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>aa</t>
+          <t>bb</t>
         </is>
       </c>
       <c r="Z7" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA7" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>aa</t>
+          <t>bb</t>
         </is>
       </c>
       <c r="AC7" t="n">
@@ -1197,11 +872,11 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1211,12 +886,12 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Wood</t>
+          <t>Water</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>None</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1268,35 +943,35 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>bb</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="Z8" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AA8" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>bb</t>
+          <t>cc</t>
         </is>
       </c>
       <c r="AC8" t="n">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="AD8" t="n">
         <v>10</v>
@@ -1304,11 +979,11 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1318,29 +993,29 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Water</t>
+          <t>Fire</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>Earth</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
           <t>None</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Control</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
         <is>
           <t>None</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
       <c r="J9" t="n">
         <v>1</v>
       </c>
@@ -1357,10 +1032,10 @@
         <v>1</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
@@ -1372,38 +1047,38 @@
         <v>1</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>dd</t>
         </is>
       </c>
       <c r="Z9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA9" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>cc</t>
+          <t>dd</t>
         </is>
       </c>
       <c r="AC9" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AD9" t="n">
         <v>10</v>
@@ -1411,11 +1086,11 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1425,12 +1100,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Fire</t>
+          <t>Earth</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1449,25 +1124,25 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="K10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="M10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="N10" t="n">
-        <v>1</v>
+        <v>100</v>
       </c>
       <c r="O10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
@@ -1479,10 +1154,10 @@
         <v>1</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1495,22 +1170,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>dd</t>
+          <t>aa</t>
         </is>
       </c>
       <c r="Z10" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AA10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>dd</t>
+          <t>aa</t>
         </is>
       </c>
       <c r="AC10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD10" t="n">
         <v>10</v>
@@ -1518,11 +1193,11 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1532,12 +1207,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Earth</t>
+          <t>Metal</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Metal</t>
+          <t>Wood</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1592,141 +1267,34 @@
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>aa</t>
+          <t>bb</t>
         </is>
       </c>
       <c r="Z11" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AA11" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>aa</t>
+          <t>bb</t>
         </is>
       </c>
       <c r="AC11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD11" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>6</v>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Metal</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Wood</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>Control</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="J12" t="n">
-        <v>100</v>
-      </c>
-      <c r="K12" t="n">
-        <v>100</v>
-      </c>
-      <c r="L12" t="n">
-        <v>100</v>
-      </c>
-      <c r="M12" t="n">
-        <v>100</v>
-      </c>
-      <c r="N12" t="n">
-        <v>100</v>
-      </c>
-      <c r="O12" t="n">
-        <v>0</v>
-      </c>
-      <c r="P12" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="n">
-        <v>1</v>
-      </c>
-      <c r="T12" t="n">
-        <v>1</v>
-      </c>
-      <c r="U12" t="n">
-        <v>1</v>
-      </c>
-      <c r="V12" t="n">
-        <v>1</v>
-      </c>
-      <c r="W12" t="n">
-        <v>1</v>
-      </c>
-      <c r="X12" t="n">
-        <v>1</v>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>bb</t>
-        </is>
-      </c>
-      <c r="Z12" t="n">
-        <v>19</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>13</v>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>bb</t>
-        </is>
-      </c>
-      <c r="AC12" t="n">
-        <v>6</v>
-      </c>
-      <c r="AD12" t="n">
         <v>10</v>
       </c>
     </row>

--- a/data/TestMultiKey.xlsx
+++ b/data/TestMultiKey.xlsx
@@ -429,7 +429,7 @@
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>immunetag1</t>
+          <t>immune_tag1</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
@@ -449,32 +449,32 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>stringkey</t>
+          <t>string_key</t>
         </is>
       </c>
       <c r="Z1" t="inlineStr">
         <is>
-          <t>uint32key</t>
+          <t>uint32_key</t>
         </is>
       </c>
       <c r="AA1" t="inlineStr">
         <is>
-          <t>in32key</t>
+          <t>int32_key</t>
         </is>
       </c>
       <c r="AB1" t="inlineStr">
         <is>
-          <t>mstringkey</t>
+          <t>m_string_key</t>
         </is>
       </c>
       <c r="AC1" t="inlineStr">
         <is>
-          <t>muint32key</t>
+          <t>m_uint32_key</t>
         </is>
       </c>
       <c r="AD1" t="inlineStr">
         <is>
-          <t>min32key</t>
+          <t>m_int32_key</t>
         </is>
       </c>
     </row>

--- a/data/TestMultiKey.xlsx
+++ b/data/TestMultiKey.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD11"/>
+  <dimension ref="A1:AG11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -477,6 +477,16 @@
           <t>m_int32_key</t>
         </is>
       </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>test_ref</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>test_refs</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -539,6 +549,16 @@
           <t>int32</t>
         </is>
       </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>repeated uint32</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -601,6 +621,16 @@
           <t>common</t>
         </is>
       </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>common</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -638,6 +668,16 @@
           <t>multi key</t>
         </is>
       </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>fk:Test</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>gfk:Test</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="F5" t="inlineStr">
@@ -655,6 +695,16 @@
           <t>等级</t>
         </is>
       </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>FK to Test table</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>GFK to Test table</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -761,6 +811,15 @@
       </c>
       <c r="AD6" t="n">
         <v>10</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="7">
@@ -869,6 +928,15 @@
       <c r="AD7" t="n">
         <v>10</v>
       </c>
+      <c r="AE7" t="n">
+        <v>2</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>3</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -975,6 +1043,15 @@
       </c>
       <c r="AD8" t="n">
         <v>10</v>
+      </c>
+      <c r="AE8" t="n">
+        <v>3</v>
+      </c>
+      <c r="AF8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AG8" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="9">

--- a/data/TestMultiKey.xlsx
+++ b/data/TestMultiKey.xlsx
@@ -638,6 +638,11 @@
           <t>multi</t>
         </is>
       </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>idx</t>
+        </is>
+      </c>
       <c r="Y4" t="inlineStr">
         <is>
           <t>key</t>
